--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G2" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H2" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L2" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="3">
@@ -816,13 +816,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cool Buzz</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-29</v>
@@ -831,25 +831,25 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Be Sweet To Me</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>2:32</v>
+        <v>2:19</v>
       </c>
       <c r="H12" t="str">
-        <v>Violet Grohl</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L12" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="13">
@@ -892,13 +892,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Better</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-29</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>U</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>2:32</v>
       </c>
       <c r="H14" t="str">
-        <v>Baauer</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L14" t="str">
-        <v>Better - Baauer</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-29</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H15" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L15" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-29</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H16" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L16" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-29</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H17" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L17" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-29</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G18" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H18" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L18" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-29</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H19" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L19" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-29</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G20" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H20" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L20" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-29</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G21" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L21" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-29</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G22" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H22" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L22" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-29</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G23" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H23" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L23" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-29</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G24" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L24" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-29</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G25" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H25" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L25" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-29</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G26" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L26" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-29</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H27" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L27" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-29</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G28" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L28" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-29</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H29" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L29" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-29</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G30" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H30" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L30" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-29</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H31" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L31" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-29</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G32" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H32" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L32" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-29</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H33" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L33" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-29</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H34" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L34" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-29</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G35" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H35" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L35" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-29</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H36" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L36" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-29</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H37" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L37" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-29</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H38" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L38" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-29</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H39" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L39" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-29</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H40" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L40" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-29</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H41" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L41" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-29</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G42" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H42" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L42" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-29</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G43" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H43" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L43" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-29</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G44" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H44" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L44" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-29</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G45" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H45" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L45" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-29</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G46" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H46" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L46" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-29</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H47" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L47" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-29</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H48" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L48" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-29</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G49" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H49" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L49" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-29</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H50" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L50" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-29</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H51" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L51" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-29</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G52" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H52" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L52" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Leave Me For Good</v>
+        <v>oh child</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-29</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:58</v>
+        <v>2:02</v>
       </c>
       <c r="H53" t="str">
-        <v>tbh</v>
+        <v>kai devega</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L53" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dance To This</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-29</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Ritual</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Icona Pop</v>
+        <v>tbh</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L54" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-29</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G55" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H55" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L55" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-29</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H56" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L56" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-29</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H57" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L57" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-29</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H58" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L58" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-29</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G59" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H59" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L59" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-29</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H60" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L60" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-29</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H61" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L61" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-29</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H62" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L62" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-29</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G63" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H63" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L63" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-29</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G64" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H64" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L64" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-29</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G65" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H65" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L65" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-29</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H66" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L66" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-29</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G67" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H67" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L67" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-29</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G68" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H68" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L68" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-29</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L69" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-29</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G70" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H70" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L70" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-29</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H71" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L71" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-29</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H72" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L72" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-29</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H73" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L73" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-29</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G74" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H74" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L74" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-29</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H75" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L75" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-29</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H76" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L76" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-29</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H77" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L77" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>No Invite</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-29</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>The Last Balloon</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G78" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Lane 8</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L78" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bando</v>
+        <v>No Invite</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-29</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>HOPE!!</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H79" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L79" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Bando</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-29</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G80" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H80" t="str">
-        <v>Duke Dumont</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L80" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Physical</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-29</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Physical - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L81" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-29</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H82" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L82" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-29</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H83" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L83" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-29</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H84" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L84" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-29</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H85" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L85" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-29</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H86" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L86" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-29</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G87" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L87" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-29</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H88" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L88" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-29</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G89" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H89" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L89" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-29</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G90" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H90" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L90" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-29</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G91" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H91" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L91" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-29</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G92" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H92" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L92" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-29</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H93" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L93" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-29</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H94" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L94" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-29</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H95" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L95" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-29</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G96" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H96" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L96" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-29</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G97" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H97" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L97" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-29</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G98" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H98" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L98" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-29</v>
@@ -4137,68 +4137,106 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G99" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H99" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L99" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>4:34</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lioness</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-30</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Victory</v>
       </c>
       <c r="G2" t="str">
-        <v>3:32</v>
+        <v>3:27</v>
       </c>
       <c r="H2" t="str">
-        <v>Maya Hawke</v>
+        <v>Madeon</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L2" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="3">
@@ -816,13 +816,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-30</v>
@@ -831,25 +831,25 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G12" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H12" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L12" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="13">
@@ -892,13 +892,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cool Buzz</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-30</v>
@@ -907,25 +907,25 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Be Sweet To Me</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:32</v>
+        <v>2:19</v>
       </c>
       <c r="H14" t="str">
-        <v>Violet Grohl</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L14" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="15">
@@ -968,13 +968,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Ride Lonesome</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-30</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G16" t="str">
-        <v>4:32</v>
+        <v>2:32</v>
       </c>
       <c r="H16" t="str">
-        <v>Beck</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L16" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-30</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H17" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L17" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-30</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L18" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-30</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G19" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H19" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L19" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-30</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H20" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L20" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-30</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G21" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H21" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L21" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-30</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G22" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H22" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L22" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-30</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G23" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H23" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L23" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-30</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H24" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L24" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-30</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G25" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L25" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-30</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H26" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L26" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-30</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G27" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L27" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-30</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H28" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L28" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-30</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G29" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H29" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L29" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-30</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L30" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-30</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G31" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L31" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-30</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H32" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L32" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-30</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G33" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H33" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L33" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-30</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H34" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L34" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-30</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H35" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L35" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-30</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G36" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H36" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L36" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-30</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H37" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L37" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-30</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H38" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L38" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-30</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H39" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L39" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-30</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H40" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L40" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-30</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H41" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L41" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-30</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H42" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L42" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-30</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G43" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H43" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L43" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-30</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G44" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L44" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-30</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G45" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L45" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-30</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G46" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H46" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L46" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-30</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G47" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H47" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L47" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-30</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H48" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L48" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-30</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H49" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L49" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-30</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G50" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H50" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L50" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-30</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H51" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L51" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-30</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H52" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L52" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-30</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G53" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H53" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L53" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Leave Me For Good</v>
+        <v>oh child</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-30</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:58</v>
+        <v>2:02</v>
       </c>
       <c r="H54" t="str">
-        <v>tbh</v>
+        <v>kai devega</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L54" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dance To This</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-30</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Ritual</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H55" t="str">
-        <v>Icona Pop</v>
+        <v>tbh</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L55" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-30</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G56" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H56" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L56" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-30</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H57" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L57" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-30</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H58" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L58" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-30</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H59" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L59" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-30</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G60" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H60" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L60" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-30</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H61" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L61" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-30</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H62" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L62" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-30</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H63" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L63" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-30</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G64" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L64" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-30</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G65" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H65" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L65" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-30</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G66" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H66" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L66" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-30</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H67" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L67" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-30</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G68" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H68" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L68" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-30</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G69" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H69" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L69" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-30</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L70" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-30</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G71" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H71" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L71" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-30</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G72" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H72" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L72" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-30</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H73" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L73" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-30</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H74" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L74" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-30</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G75" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H75" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L75" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-30</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H76" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L76" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-30</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H77" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L77" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-30</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H78" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L78" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No Invite</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-30</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>The Last Balloon</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Lane 8</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L79" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Bando</v>
+        <v>No Invite</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-30</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>HOPE!!</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G80" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H80" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L80" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Bando</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-30</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G81" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>Duke Dumont</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L81" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Physical</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-30</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Physical - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H82" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L82" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-30</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H83" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L83" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-30</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H84" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L84" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-30</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H85" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L85" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-30</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H86" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L86" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-30</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H87" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L87" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-30</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G88" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L88" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-30</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H89" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L89" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-30</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G90" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H90" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L90" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-30</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G91" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H91" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L91" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-30</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G92" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H92" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L92" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-30</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G93" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H93" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L93" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-30</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H94" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L94" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-30</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H95" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L95" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-30</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H96" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L96" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-30</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G97" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H97" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L97" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-30</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G98" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H98" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L98" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-30</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G99" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H99" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L99" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-30</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G100" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H100" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L100" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-04-30</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>4:34</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>